--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_results_adapted_algorithm_manualreview.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_results_adapted_algorithm_manualreview.xlsx
@@ -1,34 +1,330 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F30479A-71A4-D841-A12A-453E665A4507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="40" yWindow="4180" windowWidth="30240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="93">
+  <si>
+    <t>CASE_NUMBER</t>
+  </si>
+  <si>
+    <t>MANNER</t>
+  </si>
+  <si>
+    <t>CAUSE</t>
+  </si>
+  <si>
+    <t>ACCIDENT</t>
+  </si>
+  <si>
+    <t>HOMICIDE</t>
+  </si>
+  <si>
+    <t>SUICIDE</t>
+  </si>
+  <si>
+    <t>PENDING</t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>NATURAL</t>
+  </si>
+  <si>
+    <t>FINAL_OD</t>
+  </si>
+  <si>
+    <t>FINAL_COLD</t>
+  </si>
+  <si>
+    <t>FINAL_HEAT</t>
+  </si>
+  <si>
+    <t>FINAL_SUICIDE_CAUSE</t>
+  </si>
+  <si>
+    <t>FINAL_HOMICIDE_CAUSE</t>
+  </si>
+  <si>
+    <t>FINAL_OTHER_INJURY</t>
+  </si>
+  <si>
+    <t>FINAL_HEART</t>
+  </si>
+  <si>
+    <t>FINAL_COMM_DISEASE</t>
+  </si>
+  <si>
+    <t>FINAL_NON_COMM_DISEASE</t>
+  </si>
+  <si>
+    <t>FINAL_ILLNESS</t>
+  </si>
+  <si>
+    <t>FINAL_UNDETERMINED_CAUSE</t>
+  </si>
+  <si>
+    <t>CAUSE_ACCIDENTAL</t>
+  </si>
+  <si>
+    <t>CAUSE_INTENTIONAL</t>
+  </si>
+  <si>
+    <t>CAUSE_EXTERNAL</t>
+  </si>
+  <si>
+    <t>CAUSE_INTERNAL</t>
+  </si>
+  <si>
+    <t>CAUSE_UNDETERMINED</t>
+  </si>
+  <si>
+    <t>MANUAL</t>
+  </si>
+  <si>
+    <t>COD</t>
+  </si>
+  <si>
+    <t>suicide</t>
+  </si>
+  <si>
+    <t>blunt force head trauma</t>
+  </si>
+  <si>
+    <t>illness (exclude aids-related deaths), specify illness</t>
+  </si>
+  <si>
+    <t>SHOCK SYNDROME WITH HYPERTENSION RESPIRATORY DISTRESS</t>
+  </si>
+  <si>
+    <t>METASTATIC CARCINOMA OF UNKNOWN ORIGIN</t>
+  </si>
+  <si>
+    <t>OYMCHOMA CANCER</t>
+  </si>
+  <si>
+    <t>medical</t>
+  </si>
+  <si>
+    <t>hep c</t>
+  </si>
+  <si>
+    <t>natural causes/illness</t>
+  </si>
+  <si>
+    <t>natural cause</t>
+  </si>
+  <si>
+    <t>natural</t>
+  </si>
+  <si>
+    <t>COMPLICATIONS OF METASTATIC HEPATOCELLULAR CARCINOMA</t>
+  </si>
+  <si>
+    <t>blunt force head injuries homicide</t>
+  </si>
+  <si>
+    <t>natural causes</t>
+  </si>
+  <si>
+    <t>PERIFERAL VASCULAR DISEASE</t>
+  </si>
+  <si>
+    <t>MUTLI-ORGAN FAILURE DUE TO END-STAGE RENAL DISEASE</t>
+  </si>
+  <si>
+    <t>metastatic urothelial carcinoma of the renal pelvis</t>
+  </si>
+  <si>
+    <t>TERMINAL CANCER</t>
+  </si>
+  <si>
+    <t>LOBAR PNEUMONIA</t>
+  </si>
+  <si>
+    <t>ADULT FAILURE TO THRIVE SECONDARY TO MULT. COMORBIDITIES</t>
+  </si>
+  <si>
+    <t>METASTATIC BLADDER CANCER</t>
+  </si>
+  <si>
+    <t>accidental</t>
+  </si>
+  <si>
+    <t>ACUTE BRONCHOPNEUMONIA COMPLICATING INFLUENZA A INFECTION</t>
+  </si>
+  <si>
+    <t>COMPLICATIONS FROM URINARY BLADDER CANCER</t>
+  </si>
+  <si>
+    <t>ATHEROSCLEROTIC AND HYPERTENSIVE CARDIOVASCULAR DISEASE</t>
+  </si>
+  <si>
+    <t>SARCOMATOID NEOPLASM OF LIVER W/RUPTURE &amp; MASSIVE HEMOPERITONEUM</t>
+  </si>
+  <si>
+    <t>suicide (e.g. hanging, knife/cutting instrument, intentional drug overdose) – describe events</t>
+  </si>
+  <si>
+    <t>ACUTE HEPATIC FAILURE</t>
+  </si>
+  <si>
+    <t>accidental alcohol/drug intoxication (specify type)</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>respiratory failure w/hypoxia, severe sepsis</t>
+  </si>
+  <si>
+    <t>hepatocellular carcinoma</t>
+  </si>
+  <si>
+    <t>CARDIOPULMONARY ARREST SECONDARY TO ACUTE HYPOXIC RESPIRATORY FAILURE (HAD A DNR)</t>
+  </si>
+  <si>
+    <t>LIVER FAILURE</t>
+  </si>
+  <si>
+    <t>HYPERTENSIVE &amp; ARTERIOSCLEROTIC CARDIOVASCULAR DISEASE</t>
+  </si>
+  <si>
+    <t>PNEUMONIA / CONTRIBUTORY CAUSE: HYPERTENSIVE ARTERIOSCLEROTIC CARDIOVASCULAR DISEASE; DIABETES MELLI</t>
+  </si>
+  <si>
+    <t>acquired immune deficiency syndrome (aids-related)</t>
+  </si>
+  <si>
+    <t>RESPIRATORY FAILURE</t>
+  </si>
+  <si>
+    <t>MULTI ORGAN FAILURE</t>
+  </si>
+  <si>
+    <t>COMPLICATIONS OF RECTAL CARCINOMA WITH METASTASES</t>
+  </si>
+  <si>
+    <t>METASTATIC UROTHELIAL CARCINOMA</t>
+  </si>
+  <si>
+    <t>illness</t>
+  </si>
+  <si>
+    <t>pending investigation</t>
+  </si>
+  <si>
+    <t>RECENT CEREBRAL INFARCT, PROBABLE SUBACUTE ENDOCARDITIS</t>
+  </si>
+  <si>
+    <t>COMPLICATIONS OF ACUTE MYELOMONOCYTIC LEUKEMIA</t>
+  </si>
+  <si>
+    <t>WATER INTOXICATION DUE TO PSYCHOGENIC POLYDIPSIA</t>
+  </si>
+  <si>
+    <t>METASTIC PANCREATIC CANCER</t>
+  </si>
+  <si>
+    <t>NATURAL- ACUTE MYOCARDIAL INFARCTION, ATHEROSCLEROTIC CARDIOVASCULAR DISEASE</t>
+  </si>
+  <si>
+    <t>manner accurate?</t>
+  </si>
+  <si>
+    <t>cause accurate?</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>cause should be injury, external</t>
+  </si>
+  <si>
+    <t>information is vague in general, but maybe manner could be natural</t>
+  </si>
+  <si>
+    <t>manner could be natural, cause could be illness</t>
+  </si>
+  <si>
+    <t>there is no cause input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">there is no input for either </t>
+  </si>
+  <si>
+    <t>cause should be homicide</t>
+  </si>
+  <si>
+    <t>no cause information, but could be suicide</t>
+  </si>
+  <si>
+    <t>cause could be illness</t>
+  </si>
+  <si>
+    <t>"medical" is vague</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kind of </t>
+  </si>
+  <si>
+    <t>interesting because influenza and bronchi have different communicable/non-communicable status</t>
+  </si>
+  <si>
+    <t>but cause could be illness</t>
+  </si>
+  <si>
+    <t>cause should be suicide</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +342,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,161 +646,112 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AA101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AD101"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>CASE_NUMBER</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>MANNER</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>CAUSE</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ACCIDENT</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>HOMICIDE</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>SUICIDE</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>FINAL_OD</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>FINAL_COLD</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>FINAL_HEAT</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>FINAL_SUICIDE_CAUSE</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>FINAL_HOMICIDE_CAUSE</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>FINAL_OTHER_INJURY</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>FINAL_HEART</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>FINAL_COMM_DISEASE</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>FINAL_NON_COMM_DISEASE</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>FINAL_ILLNESS</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>FINAL_UNDETERMINED_CAUSE</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>CAUSE_ACCIDENTAL</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>CAUSE_INTENTIONAL</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>CAUSE_EXTERNAL</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>CAUSE_INTERNAL</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>CAUSE_UNDETERMINED</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>31997</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>suicide</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
       <c r="D2" t="b">
         <v>0</v>
       </c>
@@ -632,20 +821,23 @@
       <c r="Z2" t="b">
         <v>1</v>
       </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>27566</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>blunt force head trauma</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
@@ -715,23 +907,28 @@
       <c r="Z3" t="b">
         <v>1</v>
       </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>9676</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SHOCK SYNDROME WITH HYPERTENSION RESPIRATORY DISTRESS</t>
-        </is>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -802,23 +999,25 @@
       <c r="Z4" t="b">
         <v>0</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA4">
         <v>9</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="AB4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>14651</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>METASTATIC CARCINOMA OF UNKNOWN ORIGIN</t>
-        </is>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -889,23 +1088,25 @@
       <c r="Z5" t="b">
         <v>0</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA5">
         <v>9</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="AB5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>9245</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>OYMCHOMA CANCER</t>
-        </is>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -976,20 +1177,23 @@
       <c r="Z6" t="b">
         <v>0</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AA6">
         <v>9</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="AB6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>26035</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>medical</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
@@ -1059,20 +1263,26 @@
       <c r="Z7" t="b">
         <v>1</v>
       </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>28270</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>hep c</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
@@ -1142,20 +1352,26 @@
       <c r="Z8" t="b">
         <v>1</v>
       </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>38376</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
@@ -1225,20 +1441,26 @@
       <c r="Z9" t="b">
         <v>1</v>
       </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>21620</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>natural cause</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
@@ -1308,20 +1530,26 @@
       <c r="Z10" t="b">
         <v>1</v>
       </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>19491</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
@@ -1391,20 +1619,26 @@
       <c r="Z11" t="b">
         <v>1</v>
       </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A12">
         <v>16801</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
       <c r="D12" t="b">
         <v>0</v>
       </c>
@@ -1474,16 +1708,23 @@
       <c r="Z12" t="b">
         <v>1</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A13">
         <v>30761</v>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="b">
         <v>0</v>
       </c>
@@ -1553,23 +1794,28 @@
       <c r="Z13" t="b">
         <v>1</v>
       </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A14">
         <v>15296</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>COMPLICATIONS OF METASTATIC HEPATOCELLULAR CARCINOMA</t>
-        </is>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
@@ -1640,20 +1886,23 @@
       <c r="Z14" t="b">
         <v>0</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14">
         <v>9</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="AB14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A15">
         <v>39792</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
       <c r="D15" t="b">
         <v>0</v>
       </c>
@@ -1723,20 +1972,26 @@
       <c r="Z15" t="b">
         <v>1</v>
       </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A16">
         <v>43821</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
       <c r="D16" t="b">
         <v>0</v>
       </c>
@@ -1806,20 +2061,26 @@
       <c r="Z16" t="b">
         <v>1</v>
       </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A17">
         <v>26891</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>blunt force head injuries homicide</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
       <c r="D17" t="b">
         <v>0</v>
       </c>
@@ -1889,20 +2150,26 @@
       <c r="Z17" t="b">
         <v>1</v>
       </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A18">
         <v>18004</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
       <c r="D18" t="b">
         <v>0</v>
       </c>
@@ -1972,20 +2239,26 @@
       <c r="Z18" t="b">
         <v>1</v>
       </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>40674</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>suicide</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
       <c r="D19" t="b">
         <v>0</v>
       </c>
@@ -2055,20 +2328,26 @@
       <c r="Z19" t="b">
         <v>1</v>
       </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>31794</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>natural causes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
       <c r="D20" t="b">
         <v>0</v>
       </c>
@@ -2138,20 +2417,26 @@
       <c r="Z20" t="b">
         <v>1</v>
       </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A21">
         <v>45230</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
@@ -2221,20 +2506,26 @@
       <c r="Z21" t="b">
         <v>1</v>
       </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A22">
         <v>18011</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
       <c r="D22" t="b">
         <v>0</v>
       </c>
@@ -2304,23 +2595,28 @@
       <c r="Z22" t="b">
         <v>1</v>
       </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A23">
         <v>10812</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>PERIFERAL VASCULAR DISEASE</t>
-        </is>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>41</v>
       </c>
       <c r="D23" t="b">
         <v>0</v>
@@ -2391,23 +2687,28 @@
       <c r="Z23" t="b">
         <v>1</v>
       </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A24">
         <v>10965</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>MUTLI-ORGAN FAILURE DUE TO END-STAGE RENAL DISEASE</t>
-        </is>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
@@ -2478,20 +2779,26 @@
       <c r="Z24" t="b">
         <v>1</v>
       </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A25">
         <v>27078</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>metastatic urothelial carcinoma of the renal pelvis</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
       <c r="D25" t="b">
         <v>0</v>
       </c>
@@ -2561,23 +2868,28 @@
       <c r="Z25" t="b">
         <v>1</v>
       </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A26">
         <v>5177</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>TERMINAL CANCER</t>
-        </is>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
       </c>
       <c r="D26" t="b">
         <v>0</v>
@@ -2648,23 +2960,25 @@
       <c r="Z26" t="b">
         <v>0</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AA26">
         <v>9</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="AB26" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A27">
         <v>6250</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>LOBAR PNEUMONIA</t>
-        </is>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
       </c>
       <c r="D27" t="b">
         <v>0</v>
@@ -2735,20 +3049,23 @@
       <c r="Z27" t="b">
         <v>0</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AA27">
         <v>9</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="AB27" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A28">
         <v>37096</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
       <c r="D28" t="b">
         <v>0</v>
       </c>
@@ -2818,20 +3135,26 @@
       <c r="Z28" t="b">
         <v>1</v>
       </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A29">
         <v>39952</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
       <c r="D29" t="b">
         <v>0</v>
       </c>
@@ -2901,23 +3224,28 @@
       <c r="Z29" t="b">
         <v>1</v>
       </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A30">
         <v>13104</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>ADULT FAILURE TO THRIVE SECONDARY TO MULT. COMORBIDITIES</t>
-        </is>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>46</v>
       </c>
       <c r="D30" t="b">
         <v>0</v>
@@ -2988,23 +3316,28 @@
       <c r="Z30" t="b">
         <v>1</v>
       </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A31">
         <v>2498</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>METASTATIC BLADDER CANCER</t>
-        </is>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
       </c>
       <c r="D31" t="b">
         <v>0</v>
@@ -3075,20 +3408,23 @@
       <c r="Z31" t="b">
         <v>0</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AA31">
         <v>9</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+      <c r="AB31" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A32">
         <v>41007</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>accidental</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
@@ -3158,20 +3494,26 @@
       <c r="Z32" t="b">
         <v>1</v>
       </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A33">
         <v>25938</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>medical</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
       <c r="D33" t="b">
         <v>0</v>
       </c>
@@ -3241,23 +3583,28 @@
       <c r="Z33" t="b">
         <v>1</v>
       </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A34">
         <v>6219</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>ACUTE BRONCHOPNEUMONIA COMPLICATING INFLUENZA A INFECTION</t>
-        </is>
+      <c r="B34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
       </c>
       <c r="D34" t="b">
         <v>0</v>
@@ -3328,20 +3675,26 @@
       <c r="Z34" t="b">
         <v>0</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AA34">
         <v>8</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+      <c r="AB34" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A35">
         <v>31761</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>natural causes</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="B35" t="s">
+        <v>40</v>
+      </c>
       <c r="D35" t="b">
         <v>0</v>
       </c>
@@ -3411,23 +3764,28 @@
       <c r="Z35" t="b">
         <v>1</v>
       </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A36">
         <v>6435</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>COMPLICATIONS FROM URINARY BLADDER CANCER</t>
-        </is>
+      <c r="B36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" t="s">
+        <v>50</v>
       </c>
       <c r="D36" t="b">
         <v>0</v>
@@ -3498,23 +3856,25 @@
       <c r="Z36" t="b">
         <v>0</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AA36">
         <v>9</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+      <c r="AB36" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A37">
         <v>3115</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ATHEROSCLEROTIC AND HYPERTENSIVE CARDIOVASCULAR DISEASE</t>
-        </is>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>51</v>
       </c>
       <c r="D37" t="b">
         <v>0</v>
@@ -3585,20 +3945,23 @@
       <c r="Z37" t="b">
         <v>0</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AA37">
         <v>7</v>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+      <c r="AB37" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A38">
         <v>40702</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="B38" t="s">
+        <v>35</v>
+      </c>
       <c r="D38" t="b">
         <v>0</v>
       </c>
@@ -3668,23 +4031,28 @@
       <c r="Z38" t="b">
         <v>1</v>
       </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A39">
         <v>8820</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>SARCOMATOID NEOPLASM OF LIVER W/RUPTURE &amp; MASSIVE HEMOPERITONEUM</t>
-        </is>
+      <c r="B39" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" t="s">
+        <v>52</v>
       </c>
       <c r="D39" t="b">
         <v>0</v>
@@ -3755,20 +4123,23 @@
       <c r="Z39" t="b">
         <v>0</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AA39">
         <v>9</v>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
+      <c r="AB39" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A40">
         <v>42872</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="B40" t="s">
+        <v>35</v>
+      </c>
       <c r="D40" t="b">
         <v>0</v>
       </c>
@@ -3838,20 +4209,26 @@
       <c r="Z40" t="b">
         <v>1</v>
       </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A41">
         <v>4955</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>suicide (e.g. hanging, knife/cutting instrument, intentional drug overdose) – describe events</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
       <c r="D41" t="b">
         <v>0</v>
       </c>
@@ -3921,23 +4298,28 @@
       <c r="Z41" t="b">
         <v>1</v>
       </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A42">
         <v>687</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ACUTE HEPATIC FAILURE</t>
-        </is>
+      <c r="B42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" t="s">
+        <v>54</v>
       </c>
       <c r="D42" t="b">
         <v>0</v>
@@ -4008,20 +4390,23 @@
       <c r="Z42" t="b">
         <v>0</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AA42">
         <v>9</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
+      <c r="AB42" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A43">
         <v>40102</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="B43" t="s">
+        <v>35</v>
+      </c>
       <c r="D43" t="b">
         <v>0</v>
       </c>
@@ -4091,20 +4476,17 @@
       <c r="Z43" t="b">
         <v>1</v>
       </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
+      <c r="AA43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A44">
         <v>8545</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>accidental alcohol/drug intoxication (specify type)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="B44" t="s">
+        <v>55</v>
+      </c>
       <c r="D44" t="b">
         <v>1</v>
       </c>
@@ -4174,20 +4556,17 @@
       <c r="Z44" t="b">
         <v>1</v>
       </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
+      <c r="AA44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A45">
         <v>42334</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="B45" t="s">
+        <v>35</v>
+      </c>
       <c r="D45" t="b">
         <v>0</v>
       </c>
@@ -4257,20 +4636,17 @@
       <c r="Z45" t="b">
         <v>1</v>
       </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
+      <c r="AA45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A46">
         <v>31540</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>natural causes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="B46" t="s">
+        <v>40</v>
+      </c>
       <c r="D46" t="b">
         <v>0</v>
       </c>
@@ -4340,20 +4716,17 @@
       <c r="Z46" t="b">
         <v>1</v>
       </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
+      <c r="AA46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A47">
         <v>35043</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="B47" t="s">
+        <v>56</v>
+      </c>
       <c r="D47" t="b">
         <v>0</v>
       </c>
@@ -4423,20 +4796,17 @@
       <c r="Z47" t="b">
         <v>1</v>
       </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
+      <c r="AA47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A48">
         <v>19089</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="B48" t="s">
+        <v>37</v>
+      </c>
       <c r="D48" t="b">
         <v>0</v>
       </c>
@@ -4506,20 +4876,17 @@
       <c r="Z48" t="b">
         <v>1</v>
       </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
+      <c r="AA48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A49">
         <v>38250</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="B49" t="s">
+        <v>35</v>
+      </c>
       <c r="D49" t="b">
         <v>0</v>
       </c>
@@ -4589,20 +4956,17 @@
       <c r="Z49" t="b">
         <v>1</v>
       </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
+      <c r="AA49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A50">
         <v>17643</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="B50" t="s">
+        <v>37</v>
+      </c>
       <c r="D50" t="b">
         <v>0</v>
       </c>
@@ -4672,20 +5036,17 @@
       <c r="Z50" t="b">
         <v>1</v>
       </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
+      <c r="AA50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A51">
         <v>28555</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>respiratory failure w/hypoxia, severe sepsis</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="B51" t="s">
+        <v>57</v>
+      </c>
       <c r="D51" t="b">
         <v>0</v>
       </c>
@@ -4755,20 +5116,17 @@
       <c r="Z51" t="b">
         <v>1</v>
       </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
+      <c r="AA51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A52">
         <v>23558</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>natural causes</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="B52" t="s">
+        <v>40</v>
+      </c>
       <c r="D52" t="b">
         <v>0</v>
       </c>
@@ -4838,20 +5196,17 @@
       <c r="Z52" t="b">
         <v>1</v>
       </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
+      <c r="AA52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A53">
         <v>21312</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="B53" t="s">
+        <v>37</v>
+      </c>
       <c r="D53" t="b">
         <v>0</v>
       </c>
@@ -4921,20 +5276,17 @@
       <c r="Z53" t="b">
         <v>1</v>
       </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
+      <c r="AA53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A54">
         <v>29465</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="B54" t="s">
+        <v>37</v>
+      </c>
       <c r="D54" t="b">
         <v>0</v>
       </c>
@@ -5004,20 +5356,17 @@
       <c r="Z54" t="b">
         <v>1</v>
       </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
+      <c r="AA54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A55">
         <v>27508</v>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>hepatocellular carcinoma</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="B55" t="s">
+        <v>58</v>
+      </c>
       <c r="D55" t="b">
         <v>0</v>
       </c>
@@ -5087,20 +5436,17 @@
       <c r="Z55" t="b">
         <v>1</v>
       </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
+      <c r="AA55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A56">
         <v>37746</v>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="B56" t="s">
+        <v>35</v>
+      </c>
       <c r="D56" t="b">
         <v>0</v>
       </c>
@@ -5170,20 +5516,17 @@
       <c r="Z56" t="b">
         <v>1</v>
       </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
+      <c r="AA56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A57">
         <v>40231</v>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
       <c r="D57" t="b">
         <v>0</v>
       </c>
@@ -5253,20 +5596,17 @@
       <c r="Z57" t="b">
         <v>1</v>
       </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
+      <c r="AA57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A58">
         <v>38359</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="B58" t="s">
+        <v>35</v>
+      </c>
       <c r="D58" t="b">
         <v>0</v>
       </c>
@@ -5336,20 +5676,17 @@
       <c r="Z58" t="b">
         <v>1</v>
       </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
+      <c r="AA58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A59">
         <v>49142</v>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>natural cause</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="B59" t="s">
+        <v>36</v>
+      </c>
       <c r="D59" t="b">
         <v>0</v>
       </c>
@@ -5419,16 +5756,14 @@
       <c r="Z59" t="b">
         <v>1</v>
       </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
+      <c r="AA59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A60">
         <v>25024</v>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="b">
         <v>0</v>
       </c>
@@ -5498,20 +5833,17 @@
       <c r="Z60" t="b">
         <v>1</v>
       </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
+      <c r="AA60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A61">
         <v>35654</v>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="B61" t="s">
+        <v>35</v>
+      </c>
       <c r="D61" t="b">
         <v>0</v>
       </c>
@@ -5581,23 +5913,19 @@
       <c r="Z61" t="b">
         <v>1</v>
       </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
+      <c r="AA61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A62">
         <v>9607</v>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CARDIOPULMONARY ARREST SECONDARY TO ACUTE HYPOXIC RESPIRATORY FAILURE (HAD A DNR)</t>
-        </is>
+      <c r="B62" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" t="s">
+        <v>59</v>
       </c>
       <c r="D62" t="b">
         <v>0</v>
@@ -5668,20 +5996,17 @@
       <c r="Z62" t="b">
         <v>0</v>
       </c>
-      <c r="AA62" t="n">
+      <c r="AA62">
         <v>7</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A63">
         <v>38292</v>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+      <c r="B63" t="s">
+        <v>35</v>
+      </c>
       <c r="D63" t="b">
         <v>0</v>
       </c>
@@ -5751,20 +6076,17 @@
       <c r="Z63" t="b">
         <v>1</v>
       </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
+      <c r="AA63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A64">
         <v>18966</v>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="B64" t="s">
+        <v>37</v>
+      </c>
       <c r="D64" t="b">
         <v>0</v>
       </c>
@@ -5834,23 +6156,19 @@
       <c r="Z64" t="b">
         <v>1</v>
       </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
+      <c r="AA64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A65">
         <v>3352</v>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>LIVER FAILURE</t>
-        </is>
+      <c r="B65" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" t="s">
+        <v>60</v>
       </c>
       <c r="D65" t="b">
         <v>0</v>
@@ -5921,23 +6239,19 @@
       <c r="Z65" t="b">
         <v>1</v>
       </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
+      <c r="AA65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A66">
         <v>9914</v>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>HYPERTENSIVE &amp; ARTERIOSCLEROTIC CARDIOVASCULAR DISEASE</t>
-        </is>
+      <c r="B66" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" t="s">
+        <v>61</v>
       </c>
       <c r="D66" t="b">
         <v>0</v>
@@ -6008,23 +6322,19 @@
       <c r="Z66" t="b">
         <v>0</v>
       </c>
-      <c r="AA66" t="n">
+      <c r="AA66">
         <v>7</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A67">
         <v>263</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>PNEUMONIA / CONTRIBUTORY CAUSE: HYPERTENSIVE ARTERIOSCLEROTIC CARDIOVASCULAR DISEASE; DIABETES MELLI</t>
-        </is>
+      <c r="B67" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" t="s">
+        <v>62</v>
       </c>
       <c r="D67" t="b">
         <v>0</v>
@@ -6095,16 +6405,14 @@
       <c r="Z67" t="b">
         <v>0</v>
       </c>
-      <c r="AA67" t="n">
+      <c r="AA67">
         <v>7</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="n">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A68">
         <v>30778</v>
       </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="b">
         <v>0</v>
       </c>
@@ -6174,20 +6482,17 @@
       <c r="Z68" t="b">
         <v>1</v>
       </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
+      <c r="AA68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A69">
         <v>44172</v>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="B69" t="s">
+        <v>37</v>
+      </c>
       <c r="D69" t="b">
         <v>0</v>
       </c>
@@ -6257,16 +6562,14 @@
       <c r="Z69" t="b">
         <v>1</v>
       </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
+      <c r="AA69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A70">
         <v>46023</v>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="b">
         <v>0</v>
       </c>
@@ -6336,20 +6639,17 @@
       <c r="Z70" t="b">
         <v>1</v>
       </c>
-      <c r="AA70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
+      <c r="AA70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A71">
         <v>9651</v>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>acquired immune deficiency syndrome (aids-related)</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="B71" t="s">
+        <v>63</v>
+      </c>
       <c r="D71" t="b">
         <v>0</v>
       </c>
@@ -6419,23 +6719,19 @@
       <c r="Z71" t="b">
         <v>1</v>
       </c>
-      <c r="AA71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
+      <c r="AA71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A72">
         <v>9421</v>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>RESPIRATORY FAILURE</t>
-        </is>
+      <c r="B72" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" t="s">
+        <v>64</v>
       </c>
       <c r="D72" t="b">
         <v>0</v>
@@ -6506,23 +6802,19 @@
       <c r="Z72" t="b">
         <v>0</v>
       </c>
-      <c r="AA72" t="n">
+      <c r="AA72">
         <v>9</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A73">
         <v>11446</v>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>MULTI ORGAN FAILURE</t>
-        </is>
+      <c r="B73" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" t="s">
+        <v>65</v>
       </c>
       <c r="D73" t="b">
         <v>0</v>
@@ -6593,16 +6885,14 @@
       <c r="Z73" t="b">
         <v>1</v>
       </c>
-      <c r="AA73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
+      <c r="AA73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A74">
         <v>30777</v>
       </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="b">
         <v>0</v>
       </c>
@@ -6672,23 +6962,19 @@
       <c r="Z74" t="b">
         <v>1</v>
       </c>
-      <c r="AA74" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
+      <c r="AA74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A75">
         <v>8065</v>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>COMPLICATIONS OF RECTAL CARCINOMA WITH METASTASES</t>
-        </is>
+      <c r="B75" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" t="s">
+        <v>66</v>
       </c>
       <c r="D75" t="b">
         <v>0</v>
@@ -6759,20 +7045,17 @@
       <c r="Z75" t="b">
         <v>0</v>
       </c>
-      <c r="AA75" t="n">
+      <c r="AA75">
         <v>9</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A76">
         <v>16000</v>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+      <c r="B76" t="s">
+        <v>37</v>
+      </c>
       <c r="D76" t="b">
         <v>0</v>
       </c>
@@ -6842,23 +7125,19 @@
       <c r="Z76" t="b">
         <v>1</v>
       </c>
-      <c r="AA76" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
+      <c r="AA76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A77">
         <v>15301</v>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>METASTATIC UROTHELIAL CARCINOMA</t>
-        </is>
+      <c r="B77" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" t="s">
+        <v>67</v>
       </c>
       <c r="D77" t="b">
         <v>0</v>
@@ -6929,20 +7208,17 @@
       <c r="Z77" t="b">
         <v>0</v>
       </c>
-      <c r="AA77" t="n">
+      <c r="AA77">
         <v>9</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A78">
         <v>20258</v>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="B78" t="s">
+        <v>37</v>
+      </c>
       <c r="D78" t="b">
         <v>0</v>
       </c>
@@ -7012,16 +7288,14 @@
       <c r="Z78" t="b">
         <v>1</v>
       </c>
-      <c r="AA78" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
+      <c r="AA78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A79">
         <v>47589</v>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="b">
         <v>0</v>
       </c>
@@ -7091,20 +7365,17 @@
       <c r="Z79" t="b">
         <v>1</v>
       </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
+      <c r="AA79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A80">
         <v>32199</v>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+      <c r="B80" t="s">
+        <v>37</v>
+      </c>
       <c r="D80" t="b">
         <v>0</v>
       </c>
@@ -7174,20 +7445,17 @@
       <c r="Z80" t="b">
         <v>1</v>
       </c>
-      <c r="AA80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
+      <c r="AA80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A81">
         <v>24366</v>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>illness</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+      <c r="B81" t="s">
+        <v>68</v>
+      </c>
       <c r="D81" t="b">
         <v>0</v>
       </c>
@@ -7257,20 +7525,17 @@
       <c r="Z81" t="b">
         <v>1</v>
       </c>
-      <c r="AA81" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
+      <c r="AA81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A82">
         <v>20129</v>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>pending investigation</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+      <c r="B82" t="s">
+        <v>69</v>
+      </c>
       <c r="D82" t="b">
         <v>0</v>
       </c>
@@ -7340,20 +7605,17 @@
       <c r="Z82" t="b">
         <v>1</v>
       </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
+      <c r="AA82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A83">
         <v>18275</v>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+      <c r="B83" t="s">
+        <v>37</v>
+      </c>
       <c r="D83" t="b">
         <v>0</v>
       </c>
@@ -7423,16 +7685,14 @@
       <c r="Z83" t="b">
         <v>1</v>
       </c>
-      <c r="AA83" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
+      <c r="AA83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A84">
         <v>46242</v>
       </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="b">
         <v>0</v>
       </c>
@@ -7502,16 +7762,14 @@
       <c r="Z84" t="b">
         <v>1</v>
       </c>
-      <c r="AA84" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
+      <c r="AA84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A85">
         <v>34926</v>
       </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="b">
         <v>0</v>
       </c>
@@ -7581,20 +7839,17 @@
       <c r="Z85" t="b">
         <v>1</v>
       </c>
-      <c r="AA85" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
+      <c r="AA85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A86">
         <v>4770</v>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>accidental alcohol/drug intoxication (specify type)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+      <c r="B86" t="s">
+        <v>55</v>
+      </c>
       <c r="D86" t="b">
         <v>1</v>
       </c>
@@ -7664,23 +7919,19 @@
       <c r="Z86" t="b">
         <v>1</v>
       </c>
-      <c r="AA86" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
+      <c r="AA86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A87">
         <v>745</v>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>RECENT CEREBRAL INFARCT, PROBABLE SUBACUTE ENDOCARDITIS</t>
-        </is>
+      <c r="B87" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" t="s">
+        <v>70</v>
       </c>
       <c r="D87" t="b">
         <v>0</v>
@@ -7751,20 +8002,17 @@
       <c r="Z87" t="b">
         <v>0</v>
       </c>
-      <c r="AA87" t="n">
+      <c r="AA87">
         <v>7</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A88">
         <v>40174</v>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>natural causes/illness</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+      <c r="B88" t="s">
+        <v>35</v>
+      </c>
       <c r="D88" t="b">
         <v>0</v>
       </c>
@@ -7834,20 +8082,17 @@
       <c r="Z88" t="b">
         <v>1</v>
       </c>
-      <c r="AA88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
+      <c r="AA88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A89">
         <v>21500</v>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>natural</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+      <c r="B89" t="s">
+        <v>37</v>
+      </c>
       <c r="D89" t="b">
         <v>0</v>
       </c>
@@ -7917,20 +8162,17 @@
       <c r="Z89" t="b">
         <v>1</v>
       </c>
-      <c r="AA89" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
+      <c r="AA89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A90">
         <v>22958</v>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>suicide</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+      <c r="B90" t="s">
+        <v>27</v>
+      </c>
       <c r="D90" t="b">
         <v>0</v>
       </c>
@@ -8000,20 +8242,17 @@
       <c r="Z90" t="b">
         <v>1</v>
       </c>
-      <c r="AA90" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
+      <c r="AA90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A91">
         <v>14634</v>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>suicide (e.g. hanging, knife/cutting instrument, intentional drug overdose) – describe events</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+      <c r="B91" t="s">
+        <v>53</v>
+      </c>
       <c r="D91" t="b">
         <v>0</v>
       </c>
@@ -8083,20 +8322,17 @@
       <c r="Z91" t="b">
         <v>1</v>
       </c>
-      <c r="AA91" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
+      <c r="AA91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A92">
         <v>48780</v>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>natural cause</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+      <c r="B92" t="s">
+        <v>36</v>
+      </c>
       <c r="D92" t="b">
         <v>0</v>
       </c>
@@ -8166,23 +8402,19 @@
       <c r="Z92" t="b">
         <v>1</v>
       </c>
-      <c r="AA92" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
+      <c r="AA92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A93">
         <v>3904</v>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>COMPLICATIONS OF ACUTE MYELOMONOCYTIC LEUKEMIA</t>
-        </is>
+      <c r="B93" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93" t="s">
+        <v>71</v>
       </c>
       <c r="D93" t="b">
         <v>0</v>
@@ -8253,20 +8485,17 @@
       <c r="Z93" t="b">
         <v>0</v>
       </c>
-      <c r="AA93" t="n">
+      <c r="AA93">
         <v>9</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="n">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A94">
         <v>22066</v>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>natural cause</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+      <c r="B94" t="s">
+        <v>36</v>
+      </c>
       <c r="D94" t="b">
         <v>0</v>
       </c>
@@ -8336,23 +8565,19 @@
       <c r="Z94" t="b">
         <v>1</v>
       </c>
-      <c r="AA94" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
+      <c r="AA94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A95">
         <v>13090</v>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>WATER INTOXICATION DUE TO PSYCHOGENIC POLYDIPSIA</t>
-        </is>
+      <c r="B95" t="s">
+        <v>29</v>
+      </c>
+      <c r="C95" t="s">
+        <v>72</v>
       </c>
       <c r="D95" t="b">
         <v>0</v>
@@ -8423,20 +8648,17 @@
       <c r="Z95" t="b">
         <v>0</v>
       </c>
-      <c r="AA95" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
+      <c r="AA95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A96">
         <v>24499</v>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>natural causes</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+      <c r="B96" t="s">
+        <v>40</v>
+      </c>
       <c r="D96" t="b">
         <v>0</v>
       </c>
@@ -8506,23 +8728,19 @@
       <c r="Z96" t="b">
         <v>1</v>
       </c>
-      <c r="AA96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
+      <c r="AA96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A97">
         <v>5286</v>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>METASTIC PANCREATIC CANCER</t>
-        </is>
+      <c r="B97" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97" t="s">
+        <v>73</v>
       </c>
       <c r="D97" t="b">
         <v>0</v>
@@ -8593,16 +8811,14 @@
       <c r="Z97" t="b">
         <v>0</v>
       </c>
-      <c r="AA97" t="n">
+      <c r="AA97">
         <v>9</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="n">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A98">
         <v>46090</v>
       </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="b">
         <v>0</v>
       </c>
@@ -8672,23 +8888,19 @@
       <c r="Z98" t="b">
         <v>1</v>
       </c>
-      <c r="AA98" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
+      <c r="AA98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A99">
         <v>1403</v>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>illness (exclude aids-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>NATURAL- ACUTE MYOCARDIAL INFARCTION, ATHEROSCLEROTIC CARDIOVASCULAR DISEASE</t>
-        </is>
+      <c r="B99" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" t="s">
+        <v>74</v>
       </c>
       <c r="D99" t="b">
         <v>0</v>
@@ -8759,16 +8971,14 @@
       <c r="Z99" t="b">
         <v>0</v>
       </c>
-      <c r="AA99" t="n">
+      <c r="AA99">
         <v>7</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="n">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A100">
         <v>48083</v>
       </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="b">
         <v>0</v>
       </c>
@@ -8838,20 +9048,17 @@
       <c r="Z100" t="b">
         <v>1</v>
       </c>
-      <c r="AA100" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
+      <c r="AA100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A101">
         <v>8053</v>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>accidental alcohol/drug intoxication (specify type)</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+      <c r="B101" t="s">
+        <v>55</v>
+      </c>
       <c r="D101" t="b">
         <v>1</v>
       </c>
@@ -8921,7 +9128,7 @@
       <c r="Z101" t="b">
         <v>1</v>
       </c>
-      <c r="AA101" t="n">
+      <c r="AA101">
         <v>0</v>
       </c>
     </row>

--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_results_adapted_algorithm_manualreview.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_results_adapted_algorithm_manualreview.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F30479A-71A4-D841-A12A-453E665A4507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFD4B91-84CC-9C46-BC3C-FCF423159069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40" yWindow="4180" windowWidth="30240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="260" yWindow="760" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="97">
   <si>
     <t>CASE_NUMBER</t>
   </si>
@@ -299,6 +299,18 @@
   </si>
   <si>
     <t>cause should be suicide</t>
+  </si>
+  <si>
+    <t>cause should be overdose</t>
+  </si>
+  <si>
+    <t>final cause should be illness</t>
+  </si>
+  <si>
+    <t>manner should be natural, cause should be noncomm disease</t>
+  </si>
+  <si>
+    <t>cause could be noncomm disease</t>
   </si>
 </sst>
 </file>
@@ -4479,6 +4491,12 @@
       <c r="AA43">
         <v>0</v>
       </c>
+      <c r="AB43" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A44">
@@ -4559,6 +4577,15 @@
       <c r="AA44">
         <v>0</v>
       </c>
+      <c r="AB44" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A45">
@@ -4639,6 +4666,15 @@
       <c r="AA45">
         <v>0</v>
       </c>
+      <c r="AB45" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A46">
@@ -4719,6 +4755,12 @@
       <c r="AA46">
         <v>0</v>
       </c>
+      <c r="AB46" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A47">
@@ -4799,6 +4841,12 @@
       <c r="AA47">
         <v>0</v>
       </c>
+      <c r="AB47" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A48">
@@ -4879,8 +4927,14 @@
       <c r="AA48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB48" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>38250</v>
       </c>
@@ -4959,8 +5013,17 @@
       <c r="AA49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB49" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>17643</v>
       </c>
@@ -5039,8 +5102,14 @@
       <c r="AA50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB50" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>28555</v>
       </c>
@@ -5119,8 +5188,17 @@
       <c r="AA51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB51" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>23558</v>
       </c>
@@ -5199,8 +5277,14 @@
       <c r="AA52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB52" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>21312</v>
       </c>
@@ -5279,8 +5363,14 @@
       <c r="AA53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB53" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>29465</v>
       </c>
@@ -5359,8 +5449,14 @@
       <c r="AA54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB54" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>27508</v>
       </c>
@@ -5439,8 +5535,17 @@
       <c r="AA55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB55" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>37746</v>
       </c>
@@ -5519,8 +5624,17 @@
       <c r="AA56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB56" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>40231</v>
       </c>
@@ -5599,8 +5713,17 @@
       <c r="AA57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB57" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC57" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>38359</v>
       </c>
@@ -5679,8 +5802,17 @@
       <c r="AA58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB58" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>49142</v>
       </c>
@@ -5759,8 +5891,14 @@
       <c r="AA59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB59" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>25024</v>
       </c>
@@ -5836,8 +5974,14 @@
       <c r="AA60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB60" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC60" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>35654</v>
       </c>
@@ -5916,8 +6060,17 @@
       <c r="AA61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB61" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>9607</v>
       </c>
@@ -5999,8 +6152,14 @@
       <c r="AA62">
         <v>7</v>
       </c>
-    </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB62" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>38292</v>
       </c>
@@ -6079,8 +6238,17 @@
       <c r="AA63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB63" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC63" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>18966</v>
       </c>
@@ -6159,8 +6327,14 @@
       <c r="AA64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB64" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>3352</v>
       </c>
@@ -6242,8 +6416,17 @@
       <c r="AA65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB65" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>9914</v>
       </c>
@@ -6325,8 +6508,14 @@
       <c r="AA66">
         <v>7</v>
       </c>
-    </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB66" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>263</v>
       </c>
@@ -6408,8 +6597,14 @@
       <c r="AA67">
         <v>7</v>
       </c>
-    </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB67" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC67" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>30778</v>
       </c>
@@ -6485,8 +6680,14 @@
       <c r="AA68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB68" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC68" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>44172</v>
       </c>
@@ -6565,8 +6766,14 @@
       <c r="AA69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB69" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC69" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>46023</v>
       </c>
@@ -6642,8 +6849,14 @@
       <c r="AA70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB70" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC70" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>9651</v>
       </c>
@@ -6722,8 +6935,17 @@
       <c r="AA71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB71" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC71" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>9421</v>
       </c>
@@ -6805,8 +7027,14 @@
       <c r="AA72">
         <v>9</v>
       </c>
-    </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB72" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC72" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>11446</v>
       </c>
@@ -6888,8 +7116,17 @@
       <c r="AA73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB73" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC73" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>30777</v>
       </c>
@@ -6965,8 +7202,14 @@
       <c r="AA74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB74" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC74" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>8065</v>
       </c>
@@ -7048,8 +7291,14 @@
       <c r="AA75">
         <v>9</v>
       </c>
-    </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB75" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC75" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>16000</v>
       </c>
@@ -7128,8 +7377,14 @@
       <c r="AA76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB76" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC76" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>15301</v>
       </c>
@@ -7211,8 +7466,14 @@
       <c r="AA77">
         <v>9</v>
       </c>
-    </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB77" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>20258</v>
       </c>
@@ -7291,8 +7552,14 @@
       <c r="AA78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB78" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC78" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>47589</v>
       </c>
@@ -7368,8 +7635,14 @@
       <c r="AA79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB79" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>32199</v>
       </c>
@@ -7448,8 +7721,14 @@
       <c r="AA80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB80" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC80" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>24366</v>
       </c>
@@ -7528,8 +7807,17 @@
       <c r="AA81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB81" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC81" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>20129</v>
       </c>
@@ -7608,8 +7896,14 @@
       <c r="AA82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB82" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC82" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>18275</v>
       </c>
@@ -7688,8 +7982,14 @@
       <c r="AA83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB83" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>46242</v>
       </c>
@@ -7765,8 +8065,14 @@
       <c r="AA84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB84" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC84" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>34926</v>
       </c>
@@ -7842,8 +8148,14 @@
       <c r="AA85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB85" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>4770</v>
       </c>
@@ -7922,8 +8234,17 @@
       <c r="AA86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB86" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC86" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD86" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="87" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>745</v>
       </c>
@@ -8005,8 +8326,14 @@
       <c r="AA87">
         <v>7</v>
       </c>
-    </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB87" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC87" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>40174</v>
       </c>
@@ -8085,8 +8412,17 @@
       <c r="AA88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB88" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC88" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD88" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>21500</v>
       </c>
@@ -8165,8 +8501,14 @@
       <c r="AA89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB89" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC89" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>22958</v>
       </c>
@@ -8245,8 +8587,17 @@
       <c r="AA90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB90" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC90" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD90" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="91" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>14634</v>
       </c>
@@ -8325,8 +8676,17 @@
       <c r="AA91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB91" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC91" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD91" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="92" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>48780</v>
       </c>
@@ -8405,8 +8765,14 @@
       <c r="AA92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB92" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC92" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>3904</v>
       </c>
@@ -8488,8 +8854,14 @@
       <c r="AA93">
         <v>9</v>
       </c>
-    </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB93" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC93" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>22066</v>
       </c>
@@ -8568,8 +8940,14 @@
       <c r="AA94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB94" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC94" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>13090</v>
       </c>
@@ -8651,8 +9029,14 @@
       <c r="AA95">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB95" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC95" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="96" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>24499</v>
       </c>
@@ -8731,8 +9115,14 @@
       <c r="AA96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB96" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC96" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>5286</v>
       </c>
@@ -8814,8 +9204,14 @@
       <c r="AA97">
         <v>9</v>
       </c>
-    </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB97" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC97" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="98" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>46090</v>
       </c>
@@ -8891,8 +9287,14 @@
       <c r="AA98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB98" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC98" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>1403</v>
       </c>
@@ -8974,8 +9376,14 @@
       <c r="AA99">
         <v>7</v>
       </c>
-    </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB99" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC99" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>48083</v>
       </c>
@@ -9051,8 +9459,14 @@
       <c r="AA100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB100" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC100" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>8053</v>
       </c>
@@ -9130,6 +9544,15 @@
       </c>
       <c r="AA101">
         <v>0</v>
+      </c>
+      <c r="AB101" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC101" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD101" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
